--- a/SAKHALIN_ZAPROS/00_СВОДКА_кому_что_отправить.xlsx
+++ b/SAKHALIN_ZAPROS/00_СВОДКА_кому_что_отправить.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,14 +569,14 @@
         </is>
       </c>
       <c r="F3" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>1:1/1, 1:1/2, 1:1/3, 1:1/4, 1:1/6, 2:1/3, 2:1/4, 2:1/5, 2:1/6, 2:1/7, 2:1/8, 2:1/9, 2:1/10, 2:1/31, 2:1/57</t>
+          <t>2:1/3, 2:1/4, 2:1/5, 2:1/6, 2:1/7, 2:1/8, 2:1/9, 2:1/10, 2:1/31, 2:1/57</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+          <t>АО «ПЗТА» (Пензенский завод трубопроводной арматуры, pzta.ru)</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>+7 (4725) 469-470 (завод)</t>
+          <t>+7 (8412) 351-000</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>zavod@saz-avangard.ru</t>
+          <t>sale@pzta.ru</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="F4" s="4" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>1:1/9, 1:1/33, 1:1/58, 1:1/59, 1:1/60, 1:1/61, 1:1/63, 1:2/1, 1:2/3, 1:2/4, 1:2/5, 1:2/10, 1:2/12, 1:2/13, 2:1/11, 2:1/12, 2:1/38, 2:1/43, 2:1/44, 2:1/53, 2:1/54, 2:1/55, 2:1/56</t>
+          <t>2:1/1, 2:1/2, 2:1/67, 2:1/68, 2:1/70, 2:2/1, 2:2/2</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>02_ООО_Арма-Пром.xlsx</t>
+          <t>02_АО_ПЗТА.xlsx</t>
         </is>
       </c>
     </row>
@@ -632,17 +632,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>ООО «Торговый Дом АДЛ» (бренды «Гранвэл», «Гранлок», «Гранар», «Гранвент»)</t>
+          <t>ООО «ГАЛЛОП» (Новосибирский арматурный завод)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 937-89-68</t>
+          <t>+7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>info@adl.ru</t>
+          <t>info@gallop.ru</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -651,19 +651,19 @@
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>1:1/8, 1:1/15, 1:1/16, 1:1/17, 1:1/19, 1:1/20, 1:1/36, 1:1/42, 1:1/43, 1:1/49, 1:1/50, 1:1/51, 1:1/52, 1:2/2, 1:2/9, 1:3/1, 2:1/36, 2:1/37, 2:1/41, 2:1/42</t>
+          <t>2:1/28, 2:1/29, 2:1/30, 2:1/40, 2:2/3, 2:2/4, 2:2/5, 2:2/6, 2:2/7, 2:2/9, 2:2/10, 2:2/11, 2:2/12, 2:2/16</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>03_ООО_Торговый_Дом_АДЛ.xlsx</t>
+          <t>03_ООО_ГАЛЛОП.xlsx</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>ООО «ГАЛЛОП» (Новосибирский арматурный завод)</t>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>+7 (383) 355-10-00</t>
+          <t>+7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>info@gallop.ru</t>
+          <t>zavod@saz-avangard.ru</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -692,19 +692,19 @@
         </is>
       </c>
       <c r="F6" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1:3/2, 1:3/3, 2:1/28, 2:1/29, 2:1/30, 2:1/40, 2:2/3, 2:2/4, 2:2/5, 2:2/6, 2:2/7, 2:2/9, 2:2/10, 2:2/11, 2:2/12, 2:2/16</t>
+          <t>2:1/11, 2:1/12, 2:1/38, 2:1/43, 2:1/44, 2:1/53, 2:1/54, 2:1/55, 2:1/56</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>04_ООО_ГАЛЛОП.xlsx</t>
+          <t>04_ООО_Арма-Пром.xlsx</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
@@ -755,17 +755,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>АО «ПЗТА» (Пензенский завод трубопроводной арматуры, pzta.ru)</t>
+          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 351-000</t>
+          <t>8-800-444-74-74</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>sale@pzta.ru</t>
+          <t>info@alsoarm.ru</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -774,19 +774,15 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>2:1/1, 2:1/2, 2:1/67, 2:1/68, 2:1/70, 2:1/71, 2:2/1, 2:2/2</t>
-        </is>
-      </c>
+      <c r="H8" s="5" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>06_АО_ПЗТА.xlsx</t>
+          <t>06_ООО_АЛСО.xlsx</t>
         </is>
       </c>
     </row>
@@ -796,17 +792,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>АО «Благовещенский арматурный завод» (АО «БАЗ»)</t>
+          <t>ОАО «Литейно-механический завод» (г. Семёнов)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>+7 (34766) 2-99-10, 2-99-11</t>
+          <t>+7 (83162) 5-70-90</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>baz@bazrb.ru</t>
+          <t>marketlmz@mail.ru</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -815,19 +811,19 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>15</v>
-      </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>1:1/57</t>
+          <t>2:1/13, 2:1/14, 2:1/15, 2:1/16, 2:1/17</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>07_АО_Благовещенский_арматурный_завод.xlsx</t>
+          <t>07_ОАО_Литейно-механический_завод.xlsx</t>
         </is>
       </c>
     </row>
@@ -837,17 +833,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>ОАО «Литейно-механический завод» (г. Семёнов)</t>
+          <t>«Ярдос» (завод шаровых кранов ЗАРД/ЗАРДП; юрадрес: Химки г.о., д. Брехово, Промплощадка, стр. 2)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>+7 (83162) 5-70-90</t>
+          <t>+7 (495) 662-79-12</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>marketlmz@mail.ru</t>
+          <t>yardos@yardos.ru (заявки: ko@yardos.ru)</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -856,19 +852,19 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1:1/18, 1:1/23, 1:1/40, 1:1/41, 2:1/13, 2:1/14, 2:1/15, 2:1/16, 2:1/17</t>
+          <t>2:1/58, 2:1/59, 2:1/60, 2:1/61, 2:1/62, 2:1/63</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>08_ОАО_Литейно-механический_завод.xlsx</t>
+          <t>08_Ярдос.xlsx</t>
         </is>
       </c>
     </row>
@@ -878,17 +874,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>АО «АРМАТЭК»</t>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>+7 (812) 611-03-77</t>
+          <t>8-800-700-62-60</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>zakaz@armatek.ru</t>
+          <t>info@fobosarm.ru</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -897,19 +893,15 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>1:1/37, 1:1/38, 1:1/39, 1:1/54, 1:1/55, 1:1/56, 2:1/19, 2:1/20, 2:1/21, 2:1/22, 2:1/23, 2:1/34, 2:1/35</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>09_АО_АРМАТЭК.xlsx</t>
+          <t>09_ЗАО_Арматурная_Компания_ФОБОС.xlsx</t>
         </is>
       </c>
     </row>
@@ -919,17 +911,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
+          <t>АО «Благовещенский арматурный завод» (АО «БАЗ»)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>8-800-444-74-74</t>
+          <t>+7 (34766) 2-99-10, 2-99-11</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>info@alsoarm.ru</t>
+          <t>baz@bazrb.ru</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -938,19 +930,15 @@
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>1:2/11</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>10_ООО_АЛСО.xlsx</t>
+          <t>10_АО_Благовещенский_арматурный_завод.xlsx</t>
         </is>
       </c>
     </row>
@@ -960,17 +948,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>ООО «Инженерные системы» (ВФЗ — Владимирский фланцевый завод)</t>
+          <t>ООО «Торговый Дом АДЛ» (бренды «Гранвэл», «Гранлок», «Гранар», «Гранвент»)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 232-01-67</t>
+          <t>+7 (495) 937-89-68</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>info@vfz.su</t>
+          <t>info@adl.ru</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -979,19 +967,19 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>1:1/5, 1:1/10, 1:1/24, 1:1/25, 1:1/26, 1:1/27, 1:1/28, 1:2/6, 1:2/7, 1:2/8</t>
+          <t>2:1/36, 2:1/37, 2:1/41, 2:1/42</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>11_ООО_Инженерные_системы.xlsx</t>
+          <t>11_ООО_Торговый_Дом_АДЛ.xlsx</t>
         </is>
       </c>
     </row>
@@ -1001,17 +989,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
+          <t>«Химарматура» (Саратов, химарматура.рф)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (908) 552-12-22</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>info@aoutk.ru</t>
+          <t>info@himarm.com</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1020,15 +1008,19 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>2:1/25, 2:1/26, 2:1/27</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>12_АО_УралТехКомплектация.xlsx</t>
+          <t>12_Химарматура.xlsx</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1030,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>8-800-700-62-60</t>
+          <t>+7 (351) 307-71-09</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>info@fobosarm.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1057,19 +1049,15 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>2:1/69</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr"/>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>13_ЗАО_Арматурная_Компания_ФОБОС.xlsx</t>
+          <t>13_АО_УралТехКомплектация.xlsx</t>
         </is>
       </c>
     </row>
@@ -1079,17 +1067,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>ООО «Компания Доминик» (техническое стекло и арматура, techsteklo.ru)</t>
+          <t>ООО ПКФ «Электромагнит»</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 231-36-71</t>
+          <t>8 (800) 33-33-914</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>info@techsteklo.ru</t>
+          <t>mail@electromagnit.ru</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1098,19 +1086,19 @@
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>2:1/51</t>
+          <t>2:1/65, 2:1/66</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>14_ООО_Компания_Доминик.xlsx</t>
+          <t>14_ООО_ПКФ_Электромагнит.xlsx</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1108,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>ООО «Аквапласт» (ТМ Aquaviva, НПВХ)</t>
+          <t>ООО «Пензапромарматура» (ТМ КИПИКА)</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 255-24-23</t>
+          <t>+7 (8412) 909-200</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>info@aquaplast.ru</t>
+          <t>b18bk@11b18bk.ru</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1139,19 +1127,15 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>1:1/21, 1:1/22, 1:1/44, 1:1/45, 1:1/46, 1:1/47</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>15_ООО_Аквапласт.xlsx</t>
+          <t>15_ООО_Пензапромарматура.xlsx</t>
         </is>
       </c>
     </row>
@@ -1161,17 +1145,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>«Ярдос» (завод шаровых кранов ЗАРД/ЗАРДП; юрадрес: Химки г.о., д. Брехово, Промплощадка, стр. 2)</t>
+          <t>ООО ПНФ «ЛГ автоматика»</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>+7 (495) 662-79-12</t>
+          <t>+7 (495) 788-68-21</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>yardos@yardos.ru (заявки: ko@yardos.ru)</t>
+          <t>info@klapan.ru</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -1180,19 +1164,19 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>2:1/58, 2:1/59, 2:1/60, 2:1/61, 2:1/62, 2:1/63</t>
+          <t>2:1/24</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>16_Ярдос.xlsx</t>
+          <t>16_ООО_ПНФ_ЛГ_автоматика.xlsx</t>
         </is>
       </c>
     </row>
@@ -1202,17 +1186,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>ООО «Таганрогский котельный завод» (ООО «ТКЗ»)</t>
+          <t>АО НПО «УНИХИМТЕК» (ТМ «Графлекс»)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>+7 (8634) 341-923</t>
+          <t>+7 (495) 580-38-98</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>info@tena-tkz.ru</t>
+          <t>info@graflex.ru</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1221,19 +1205,19 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>1:1/11, 1:1/12, 1:1/65, 2:1/52</t>
+          <t>2:1/32</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>17_ООО_Таганрогский_котельный_завод.xlsx</t>
+          <t>17_АО_НПО_УНИХИМТЕК.xlsx</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1227,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>ООО «Пензапромарматура» (ТМ КИПИКА)</t>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>+7 (8412) 909-200</t>
+          <t>8 800 444-00-28</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>b18bk@11b18bk.ru</t>
+          <t>sales@ptpa.ru</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1262,19 +1246,15 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>1:1/48, 1:1/62</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>18_ООО_Пензапромарматура.xlsx</t>
+          <t>18_АО_Пензтяжпромарматура.xlsx</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1264,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>ООО ПКФ «Электромагнит»</t>
+          <t>ООО «Гималаи» (Самара)</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>8 (800) 33-33-914</t>
+          <t>8-800-201-83-41</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>mail@electromagnit.ru</t>
+          <t>gimalai@gimalai.com</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1303,524 +1283,40 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2:1/65, 2:1/66</t>
+          <t>2:2/8</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>19_ООО_ПКФ_Электромагнит.xlsx</t>
+          <t>19_ООО_Гималаи.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>АО «АБС ЗЭиМ Автоматизация»</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>+7 (8352) 30-51-48</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>sales@zeim.ru</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>1:1/53, 1:1/67, 2:1/33, 2:1/64</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>20_АО_АБС_ЗЭиМ_Автоматизация.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>«Химарматура» (Саратов, химарматура.рф)</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>+7 (908) 552-12-22</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>info@himarm.com</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>2:1/25, 2:1/26, 2:1/27</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>21_Химарматура.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>8 800 444-00-28</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>sales@ptpa.ru</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>1:1/64</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>22_АО_Пензтяжпромарматура.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>ПЭК — «Поволжская Электротехническая Компания»</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>+7 (8352) 57-05-16</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>info@piek.ru</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>23_ПЭК_Поволжская_Электротехническая_Компан.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Архимед» (бренды «Архимед», «СЕВЕР»)</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>+7 (495) 105-70-77</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>info@arhimed.tech</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>1:1/13, 1:1/14</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>24_ООО_Архимед.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>ООО «ЭнергоПромАтомСервис» (ООО «ЭПАС»)</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>+7 (343) 211-02-63</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>epas-z@mail.ru</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>1:1/34, 1:1/35</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>25_ООО_ЭнергоПромАтомСервис.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Транс-Энерго» / ООО «Лидер-Энерго»</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>+7 (8482) 21-66-32</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>trans-energo@bk.ru</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>26_ООО_Транс-Энерго_ООО_Лидер-Энерго.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>ООО «ЭНКО Проф»</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>8-800-101-51-64</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>info@enkoprof.ru</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>1:1/7</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>27_ООО_ЭНКО_Проф.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Барнаульский котельный завод» (ООО «БКЗ»)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>+7 (3852) 22-32-67 (отдел продаж)</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>bkz@bkzn.ru</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>1:1/66</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>28_ООО_Барнаульский_котельный_завод.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>ООО ПНФ «ЛГ автоматика»</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>+7 (495) 788-68-21</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>info@klapan.ru</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>2:1/24</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>29_ООО_ПНФ_ЛГ_автоматика.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>АО НПО «УНИХИМТЕК» (ТМ «Графлекс»)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>+7 (495) 580-38-98</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>info@graflex.ru</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>2:1/32</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>30_АО_НПО_УНИХИМТЕК.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>ООО «Гималаи» (Самара)</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>8-800-201-83-41</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>gimalai@gimalai.com</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>да</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>2:2/8</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>31_ООО_Гималаи.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr"/>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr"/>
-      <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="7" t="n">
-        <v>163</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>123</v>
-      </c>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1834,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1880,194 +1376,82 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>ПАРТИЯ № 1</t>
+          <t>ПАРТИЯ № 2</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Шар сталь+NBR 3010.СB02 для обратного клапана Ду 100 Benarmo арт.019-3035</t>
+          <t>Сепаратор грязи Flamco Clean Smart 3/4 FL 30021</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>ЗИП (шар) к импортному обратному клапану Benarmo арт.019-30xx; российский изготовитель совместимых шаров не найден. Вариант: заменить клапан на рос. аналог (см. обратные клапаны Гранлок/АДЛ) или запросить шар у дистрибьютора Benarmo с подтверждением происхождения.</t>
+          <t>Flamco (Нидерланды) — импорт. Российского изготовителя сепараторов грязи/воздуха с сайтом и подтверждением РФ-производства не найдено (STOUT/ROMMER/Valtec/GAOBO — импорт). Нужен отдельный поиск или замена на рос. грязевик/фильтр.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>ПАРТИЯ № 1</t>
+          <t>ПАРТИЯ № 2</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Шар сталь+NBR 3010.СB02 для обратного клапана Ду 80 Benarmo арт.019-3034</t>
+          <t>Сепаратор воздуха и шлама Flamco Flamcovent Clean Smart 3/4, 30041</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>ЗИП (шар) к импортному обратному клапану Benarmo арт.019-30xx; российский изготовитель совместимых шаров не найден. Вариант: заменить клапан на рос. аналог (см. обратные клапаны Гранлок/АДЛ) или запросить шар у дистрибьютора Benarmo с подтверждением происхождения.</t>
+          <t>Flamco (Нидерланды) — импорт. Российского изготовителя сепараторов грязи/воздуха с сайтом и подтверждением РФ-производства не найдено (STOUT/ROMMER/Valtec/GAOBO — импорт). Нужен отдельный поиск или замена на рос. грязевик/фильтр.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>11201</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>ПАРТИЯ № 1</t>
+          <t>ПАРТИЯ № 2</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Шар сталь+NBR 3010.СB02 для обратного клапана Ду 65 Benarmo арт.019-3033</t>
+          <t>Коллектор с кранами (3/4"; 3 х 1/2") Valtec VTc.580.N.0503 78753</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>ЗИП (шар) к импортному обратному клапану Benarmo арт.019-30xx; российский изготовитель совместимых шаров не найден. Вариант: заменить клапан на рос. аналог (см. обратные клапаны Гранлок/АДЛ) или запросить шар у дистрибьютора Benarmo с подтверждением происхождения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>11201</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>ПАРТИЯ № 1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Шар сталь+NBR 3010.СB02 для обратного клапана Ду 50 Benarmo арт.019-3032</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>ЗИП (шар) к импортному обратному клапану Benarmo арт.019-30xx; российский изготовитель совместимых шаров не найден. Вариант: заменить клапан на рос. аналог (см. обратные клапаны Гранлок/АДЛ) или запросить шар у дистрибьютора Benarmo с подтверждением происхождения.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>ПАРТИЯ № 2</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>Сепаратор грязи Flamco Clean Smart 3/4 FL 30021</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>Flamco (Нидерланды) — импорт. Российского изготовителя сепараторов грязи/воздуха с сайтом и подтверждением РФ-производства не найдено (STOUT/ROMMER/Valtec/GAOBO — импорт). Нужен отдельный поиск или замена на рос. грязевик/фильтр.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>ПАРТИЯ № 2</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>Сепаратор воздуха и шлама Flamco Flamcovent Clean Smart 3/4, 30041</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Flamco (Нидерланды) — импорт. Российского изготовителя сепараторов грязи/воздуха с сайтом и подтверждением РФ-производства не найдено (STOUT/ROMMER/Valtec/GAOBO — импорт). Нужен отдельный поиск или замена на рос. грязевик/фильтр.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>11202</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>ПАРТИЯ № 2</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>Коллектор с кранами (3/4"; 3 х 1/2") Valtec VTc.580.N.0503 78753</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Valtec — импорт. Российского изготовителя латунных коллекторов с шаровыми кранами не найдено (STOUT, TIEMME — Италия; прочие — Китай). Вариант: сборка из рос. латунных кранов/тройников ГАЛЛОП или LD Pride — согласовать.</t>
         </is>
